--- a/output/roomself_excel/12035.xlsx
+++ b/output/roomself_excel/12035.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>283776</v>
+        <v>49020</v>
       </c>
       <c r="D2" t="n">
-        <v>4856</v>
+        <v>1772</v>
       </c>
       <c r="E2" t="n">
-        <v>833</v>
+        <v>269</v>
       </c>
       <c r="F2" t="n">
-        <v>517</v>
+        <v>257</v>
       </c>
     </row>
     <row r="3">
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21518</v>
+        <v>234756</v>
       </c>
       <c r="D3" t="n">
-        <v>1236</v>
+        <v>4600</v>
       </c>
       <c r="E3" t="n">
-        <v>245</v>
+        <v>576</v>
       </c>
       <c r="F3" t="n">
-        <v>129</v>
+        <v>517</v>
       </c>
     </row>
     <row r="4">
@@ -514,15 +514,37 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>21518</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1236</v>
+      </c>
+      <c r="E4" t="n">
+        <v>245</v>
+      </c>
+      <c r="F4" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
         <v>4590</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D5" t="n">
         <v>564</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E5" t="n">
         <v>90</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F5" t="n">
         <v>42</v>
       </c>
     </row>

--- a/output/roomself_excel/12035.xlsx
+++ b/output/roomself_excel/12035.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:V5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,92 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_4</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_4</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_5</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_5</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_5</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_6</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_6</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_6</t>
         </is>
       </c>
     </row>
@@ -475,12 +555,40 @@
       <c r="D2" t="n">
         <v>1772</v>
       </c>
-      <c r="E2" t="n">
-        <v>269</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>257</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="G2" t="n">
+        <v>41</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>228</v>
+      </c>
+      <c r="J2" t="n">
+        <v>42</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,11 +605,71 @@
       <c r="D3" t="n">
         <v>4600</v>
       </c>
-      <c r="E3" t="n">
-        <v>576</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>517</v>
+        <v>217</v>
+      </c>
+      <c r="G3" t="n">
+        <v>30</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>546</v>
+      </c>
+      <c r="J3" t="n">
+        <v>41</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>87</v>
+      </c>
+      <c r="M3" t="n">
+        <v>18</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>85</v>
+      </c>
+      <c r="P3" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>83</v>
+      </c>
+      <c r="S3" t="n">
+        <v>39</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="U3" t="n">
+        <v>412</v>
+      </c>
+      <c r="V3" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="4">
@@ -519,12 +687,40 @@
       <c r="D4" t="n">
         <v>1236</v>
       </c>
-      <c r="E4" t="n">
-        <v>245</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>129</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="G4" t="n">
+        <v>23</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>106</v>
+      </c>
+      <c r="J4" t="n">
+        <v>42</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +737,32 @@
       <c r="D5" t="n">
         <v>564</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>90</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>42</v>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
